--- a/users.xlsx
+++ b/users.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1299FE-8297-5145-9F13-31E6D633DFF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FDEE7CD-6592-8C40-BF96-1656B8F1EEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{C3F29955-7B13-B649-9004-C0E0FC1BB1E3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
   <si>
     <t>name</t>
   </si>
@@ -50,59 +50,72 @@
     <t>role</t>
   </si>
   <si>
+    <t>editor</t>
+  </si>
+  <si>
+    <t>王五</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>李四</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张三</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Iris</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>editor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jayden</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jordan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leo Liu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lily</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Linda</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monica</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cassie</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陆总</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>admin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>viewer</t>
-  </si>
-  <si>
-    <t>editor</t>
-  </si>
-  <si>
-    <t>王五</t>
-  </si>
-  <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>李四</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>张三</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Iris</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>editor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Jayden</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Jordan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Leo Liu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lily</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Linda</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Monica</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RSH</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -487,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63BC0AE1-2C94-EA48-B123-08469EDFAC08}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="6.83203125" bestFit="1" customWidth="1"/>
@@ -512,7 +525,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B2">
         <v>1001</v>
@@ -521,12 +534,12 @@
         <v>13800000001</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>1002</v>
@@ -535,12 +548,12 @@
         <v>13800000002</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>1003</v>
@@ -549,12 +562,12 @@
         <v>13800000003</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>1004</v>
@@ -563,12 +576,12 @@
         <v>13800000004</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>1005</v>
@@ -577,12 +590,12 @@
         <v>13800000005</v>
       </c>
       <c r="D6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>1006</v>
@@ -591,12 +604,12 @@
         <v>13800000006</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>1007</v>
@@ -605,12 +618,12 @@
         <v>13800000007</v>
       </c>
       <c r="D8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>1008</v>
@@ -619,12 +632,12 @@
         <v>13800000008</v>
       </c>
       <c r="D9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>1009</v>
@@ -633,12 +646,12 @@
         <v>13800000009</v>
       </c>
       <c r="D10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>1010</v>
@@ -647,12 +660,12 @@
         <v>13800000010</v>
       </c>
       <c r="D11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>1011</v>
@@ -661,7 +674,35 @@
         <v>13800000011</v>
       </c>
       <c r="D12" t="s">
-        <v>5</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13">
+        <v>1012</v>
+      </c>
+      <c r="C13">
+        <v>13800000012</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>1013</v>
+      </c>
+      <c r="C14">
+        <v>13800000013</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/users.xlsx
+++ b/users.xlsx
@@ -2,20 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Downloads/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FDEE7CD-6592-8C40-BF96-1656B8F1EEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC03516-6B16-C846-9621-E2E8C982B2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{C3F29955-7B13-B649-9004-C0E0FC1BB1E3}"/>
+    <workbookView xWindow="20" yWindow="600" windowWidth="28800" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,99 +31,547 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>phone</t>
-  </si>
-  <si>
-    <t>role</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="129">
+  <si>
+    <t>序号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中文名</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Full Name 
+(First/Middle/Last)</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>手机号</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>李娟</t>
+  </si>
+  <si>
+    <t>Judy Li</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>judy.li@colliers.com</t>
+  </si>
+  <si>
+    <t>13901292865</t>
+  </si>
+  <si>
+    <t>祝傲</t>
+  </si>
+  <si>
+    <t>Alex Zhu</t>
+  </si>
+  <si>
+    <t>M</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Director</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>alex.zhu@colliers.com</t>
+  </si>
+  <si>
+    <t>徐坚</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jian Xu</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Manager</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>jian.xu@colliers.com</t>
+  </si>
+  <si>
+    <t>18910280991</t>
+  </si>
+  <si>
+    <t>刘谨赫</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leo Liu</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>M</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Associate Director</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>leo.liu@colliers.com</t>
+  </si>
+  <si>
+    <t>18519772868</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>殷子龙</t>
+  </si>
+  <si>
+    <t>Rocky Yin</t>
+  </si>
+  <si>
+    <t>Senior Director</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>rocky.yin@colliers.com</t>
+  </si>
+  <si>
+    <t>13466667867</t>
+  </si>
+  <si>
+    <t>闫涛</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tony Yan</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Director</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>tony.yan@colliers.com</t>
+  </si>
+  <si>
+    <t>18510399997</t>
+  </si>
+  <si>
+    <t>康磊</t>
+  </si>
+  <si>
+    <t>Jayden Kang</t>
+  </si>
+  <si>
+    <t>jayden.kang@colliers.com</t>
+  </si>
+  <si>
+    <t>15110192986</t>
+  </si>
+  <si>
+    <t>刘义思</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Iris Liu</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assistant Manager</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>iris.liu@colliers.com</t>
+  </si>
+  <si>
+    <t>郭梓芃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Niko Guo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>M</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>niko.guo@colliers.com</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>13488830494</t>
+  </si>
+  <si>
+    <t>刘韵清</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lily Liu</t>
+  </si>
+  <si>
+    <t>lily.liu@colliers.com</t>
+  </si>
+  <si>
+    <t>李嘉卉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chris Li</t>
+  </si>
+  <si>
+    <t>chris.li@colliers.com</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>郭婷婷</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monica Guo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Senior Manager</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>monica.guo@colliers.com</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>翟雨楠</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cecelia Zhai</t>
+  </si>
+  <si>
+    <t>Senior Associate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>cecelia.zhai@colliers.com</t>
+  </si>
+  <si>
+    <t>毛婷婷</t>
+  </si>
+  <si>
+    <t>Miranda Mao</t>
+  </si>
+  <si>
+    <t>miranda.mao@colliers.com</t>
+  </si>
+  <si>
+    <t>13683545645</t>
+  </si>
+  <si>
+    <t>杨凤霞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Linda Yang</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>linda.yang@colliers.com</t>
+  </si>
+  <si>
+    <t>刘瑞京</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max Liu</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>max.liu@colliers.com</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>13520050670</t>
+  </si>
+  <si>
+    <t>徐荣卿</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reuben Xu</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>reuben.xu@colliers.com</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>13401131548</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>荣宇鹏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Titus Rong</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>titus.rong@colliers.com</t>
+  </si>
+  <si>
+    <t>15901110123</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>代威</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>David Dai</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>david.dai@colliers.com</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>18810706625</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>陆明</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ming Lu</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ming.lu@colliers.com</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>高心悦</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cassie Gao</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cassie.gao@colliers.com</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>15620895791</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>王楚涵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hannah Wang</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hannah.wang@colliers.com</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>13426432808</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>15811250697</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>邮箱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（即姓名）</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>COS8244</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>内部号码（COS+手机后四位）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LM006688</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COS0991</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COS2868</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CJL292865</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COS7867</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COS9997</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COS2986</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COS2779</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COS0494</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COS0654</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COS3798</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COS9613</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COS1029</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COS5645</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COS6940</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COS0670</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COS1548</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COS0123</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COS6625</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COS2808</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Managing Director l Beijing</t>
+  </si>
+  <si>
+    <t>Role</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>editor</t>
-  </si>
-  <si>
-    <t>王五</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>admin</t>
-  </si>
-  <si>
-    <t>李四</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>张三</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Iris</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>editor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Jayden</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Jordan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Leo Liu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lily</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Linda</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Monica</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RSH</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cassie</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>陆总</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>admin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>viewer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="[$-409]mmm\-yy;@"/>
+  </numFmts>
+  <fonts count="11">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Open Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -139,16 +582,78 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Noto Sans SC"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Noto Sans SC"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Open Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Open Sans"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -156,21 +661,103 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -184,7 +771,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -499,215 +1086,1051 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63BC0AE1-2C94-EA48-B123-08469EDFAC08}">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1881D26D-58E6-4B13-B3DA-2DFBBC0E86E2}">
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.1640625" customWidth="1"/>
+    <col min="8" max="8" width="16.1640625" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" ht="32">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="H2" s="9">
+        <v>15210628244</v>
+      </c>
+      <c r="I2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B2">
-        <v>1001</v>
-      </c>
-      <c r="C2">
-        <v>13800000001</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="F3" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
+      <c r="G3" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B3">
-        <v>1002</v>
-      </c>
-      <c r="C3">
-        <v>13800000002</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H8" s="9">
+        <v>17610772779</v>
+      </c>
+      <c r="I8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H10" s="9">
+        <v>18611510654</v>
+      </c>
+      <c r="I10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" s="9">
+        <v>17553833798</v>
+      </c>
+      <c r="I11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H12" s="9">
+        <v>18910329613</v>
+      </c>
+      <c r="I12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H13" s="9">
+        <v>13911111029</v>
+      </c>
+      <c r="I13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H15" s="9">
+        <v>13381036940</v>
+      </c>
+      <c r="I15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="I17" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I19" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I20" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1003</v>
-      </c>
-      <c r="C4">
-        <v>13800000003</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="B21" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="I21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" s="6"/>
+      <c r="H22" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
+      <c r="C23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
-        <v>1004</v>
-      </c>
-      <c r="C5">
-        <v>13800000004</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="G23" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H23" s="9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6">
-        <v>1005</v>
-      </c>
-      <c r="C6">
-        <v>13800000005</v>
-      </c>
-      <c r="D6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>1006</v>
-      </c>
-      <c r="C7">
-        <v>13800000006</v>
-      </c>
-      <c r="D7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8">
-        <v>1007</v>
-      </c>
-      <c r="C8">
-        <v>13800000007</v>
-      </c>
-      <c r="D8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9">
-        <v>1008</v>
-      </c>
-      <c r="C9">
-        <v>13800000008</v>
-      </c>
-      <c r="D9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10">
-        <v>1009</v>
-      </c>
-      <c r="C10">
-        <v>13800000009</v>
-      </c>
-      <c r="D10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11">
-        <v>1010</v>
-      </c>
-      <c r="C11">
-        <v>13800000010</v>
-      </c>
-      <c r="D11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12">
-        <v>1011</v>
-      </c>
-      <c r="C12">
-        <v>13800000011</v>
-      </c>
-      <c r="D12" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13">
-        <v>1012</v>
-      </c>
-      <c r="C13">
-        <v>13800000012</v>
-      </c>
-      <c r="D13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14">
-        <v>1013</v>
-      </c>
-      <c r="C14">
-        <v>13800000013</v>
-      </c>
-      <c r="D14" t="s">
-        <v>21</v>
+      <c r="I23" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="E1">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:D1 F1:I1">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="F16" r:id="rId1" xr:uid="{BB085E9E-FFCD-405C-9F94-E947BA51B855}"/>
+    <hyperlink ref="F11" r:id="rId2" xr:uid="{B5EC9D6A-23D4-45B7-B218-F9116E3C2FC6}"/>
+    <hyperlink ref="F12" r:id="rId3" xr:uid="{9AEF8D48-4484-4DB2-8449-E5A32CA3755C}"/>
+    <hyperlink ref="F9" r:id="rId4" xr:uid="{A03950D5-0780-4D1F-87A5-AFB395C5D084}"/>
+    <hyperlink ref="F17" r:id="rId5" xr:uid="{23EFFCE7-8881-4EE5-AF6D-62B69E4B3454}"/>
+    <hyperlink ref="F19" r:id="rId6" xr:uid="{081DB404-FD40-417A-9F8B-81F9679D3428}"/>
+    <hyperlink ref="F22" r:id="rId7" xr:uid="{B9EEF2A8-C323-43A0-8DA7-D07FBBD8A3C3}"/>
+    <hyperlink ref="F20" r:id="rId8" xr:uid="{20E5CA52-45F2-41B9-86A7-4DC99EC8F684}"/>
+    <hyperlink ref="F21" r:id="rId9" xr:uid="{160233A7-DBBE-4E0E-B93C-C212C70C0B83}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup orientation="portrait" r:id="rId10"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BC605E6093A30A479FED397EFA867E40" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55774fc2038cb4dae8fef12431c133f2">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f655991e-a262-4cc2-969f-4b8d0db6a5de" xmlns:ns3="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="31482a63ce11ed8a627351d2502cc05d" ns2:_="" ns3:_="">
+    <xsd:import namespace="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
+    <xsd:import namespace="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f655991e-a262-4cc2-969f-4b8d0db6a5de" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="22" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{8f2ff732-98c2-48c5-8f70-155633f64b93}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="f655991e-a262-4cc2-969f-4b8d0db6a5de">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="18" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="7ce671e0-2aae-4c8d-b367-8bb3494c1b07" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="23" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f655991e-a262-4cc2-969f-4b8d0db6a5de" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
+</file>
+
+<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
+<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"blankspreadsheet","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDD333F8-AAE5-488E-AC14-BCEB9F667CC9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
+    <ds:schemaRef ds:uri="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E48FA878-1873-4E78-9DF6-64F409202FFB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{106A4909-FA24-4E21-8A33-CA1651A78349}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a"/>
+    <ds:schemaRef ds:uri="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D06B2AC5-E0B1-41AB-AC8C-223291054D71}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1DE854-5CA9-468B-A115-103B8CD51770}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{8c970d48-f7b9-48b0-9606-072fbefb514d}" enabled="1" method="Standard" siteId="{049e3382-8cdc-477b-9317-951b04689668}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/users.xlsx
+++ b/users.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC03516-6B16-C846-9621-E2E8C982B2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E077081-C1C2-CC40-8A0D-3A49410D2B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="600" windowWidth="28800" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="133">
   <si>
     <t>序号</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -544,6 +544,22 @@
   </si>
   <si>
     <t>admin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>余航</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ron Yu</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Intern</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>intern.bjres@colliers.com</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -692,7 +708,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -729,6 +745,18 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1087,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1881D26D-58E6-4B13-B3DA-2DFBBC0E86E2}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -1766,13 +1794,42 @@
         <v>127</v>
       </c>
     </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="12">
+        <v>23</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="G24">
+        <v>123456</v>
+      </c>
+      <c r="H24">
+        <v>18801376617</v>
+      </c>
+      <c r="I24" t="s">
+        <v>128</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="A1:D1 F1:I1">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:D1 F1:I1">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="F16" r:id="rId1" xr:uid="{BB085E9E-FFCD-405C-9F94-E947BA51B855}"/>
@@ -1784,13 +1841,38 @@
     <hyperlink ref="F22" r:id="rId7" xr:uid="{B9EEF2A8-C323-43A0-8DA7-D07FBBD8A3C3}"/>
     <hyperlink ref="F20" r:id="rId8" xr:uid="{20E5CA52-45F2-41B9-86A7-4DC99EC8F684}"/>
     <hyperlink ref="F21" r:id="rId9" xr:uid="{160233A7-DBBE-4E0E-B93C-C212C70C0B83}"/>
+    <hyperlink ref="F24" r:id="rId10" xr:uid="{31B3FE49-1511-1541-BD48-B8F1EE9A3E05}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId10"/>
+  <pageSetup orientation="portrait" r:id="rId11"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f655991e-a262-4cc2-969f-4b8d0db6a5de" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BC605E6093A30A479FED397EFA867E40" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55774fc2038cb4dae8fef12431c133f2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f655991e-a262-4cc2-969f-4b8d0db6a5de" xmlns:ns3="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="31482a63ce11ed8a627351d2502cc05d" ns2:_="" ns3:_="">
     <xsd:import namespace="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
@@ -2051,35 +2133,36 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="f655991e-a262-4cc2-969f-4b8d0db6a5de" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
-</file>
-
 <file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
 <TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"blankspreadsheet","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D06B2AC5-E0B1-41AB-AC8C-223291054D71}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{106A4909-FA24-4E21-8A33-CA1651A78349}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a"/>
+    <ds:schemaRef ds:uri="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E48FA878-1873-4E78-9DF6-64F409202FFB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDD333F8-AAE5-488E-AC14-BCEB9F667CC9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2098,31 +2181,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E48FA878-1873-4E78-9DF6-64F409202FFB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{106A4909-FA24-4E21-8A33-CA1651A78349}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a"/>
-    <ds:schemaRef ds:uri="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D06B2AC5-E0B1-41AB-AC8C-223291054D71}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1DE854-5CA9-468B-A115-103B8CD51770}">
   <ds:schemaRefs/>

--- a/users.xlsx
+++ b/users.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E077081-C1C2-CC40-8A0D-3A49410D2B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3A0063-6C34-0441-88E1-F909F00F84CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="137">
   <si>
     <t>序号</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -48,10 +48,6 @@
       <t>中文名</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Full Name 
-(First/Middle/Last)</t>
   </si>
   <si>
     <t>Gender</t>
@@ -560,6 +556,27 @@
   </si>
   <si>
     <t>intern.bjres@colliers.com</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Full Name 
+(First/Middle/Last)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>张锐捷</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jerry Zhang</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InternBoss</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>123456@colliers.com</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1115,7 +1132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1881D26D-58E6-4B13-B3DA-2DFBBC0E86E2}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -1137,25 +1154,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="I1" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1163,28 +1180,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="G2" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H2" s="9">
         <v>15210628244</v>
       </c>
       <c r="I2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1192,28 +1209,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>21</v>
-      </c>
       <c r="I3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1221,28 +1238,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="H4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>27</v>
-      </c>
       <c r="I4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1250,28 +1267,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>32</v>
-      </c>
       <c r="I5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1279,28 +1296,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="H6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>37</v>
-      </c>
       <c r="I6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1308,28 +1325,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="6" t="s">
+      <c r="G7" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H7" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>41</v>
-      </c>
       <c r="I7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1337,28 +1354,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>46</v>
-      </c>
       <c r="G8" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H8" s="9">
         <v>17610772779</v>
       </c>
       <c r="I8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1366,28 +1383,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="6" t="s">
+      <c r="G9" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H9" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>51</v>
-      </c>
       <c r="I9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1395,28 +1412,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>54</v>
-      </c>
       <c r="G10" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H10" s="9">
         <v>18611510654</v>
       </c>
       <c r="I10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1424,28 +1441,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>57</v>
-      </c>
       <c r="G11" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H11" s="9">
         <v>17553833798</v>
       </c>
       <c r="I11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1453,28 +1470,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>61</v>
-      </c>
       <c r="G12" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H12" s="9">
         <v>18910329613</v>
       </c>
       <c r="I12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1482,28 +1499,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>65</v>
-      </c>
       <c r="G13" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H13" s="9">
         <v>13911111029</v>
       </c>
       <c r="I13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1511,28 +1528,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="6" t="s">
+      <c r="G14" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H14" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>69</v>
-      </c>
       <c r="I14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1540,28 +1557,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>73</v>
-      </c>
       <c r="G15" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H15" s="9">
         <v>13381036940</v>
       </c>
       <c r="I15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1569,28 +1586,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="D16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="6" t="s">
+      <c r="G16" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H16" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>77</v>
-      </c>
       <c r="I16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1598,28 +1615,28 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" s="6" t="s">
+      <c r="G17" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H17" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="G17" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>81</v>
-      </c>
       <c r="I17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1627,28 +1644,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="6" t="s">
+      <c r="G18" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H18" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>85</v>
-      </c>
       <c r="I18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1656,28 +1673,28 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" s="6" t="s">
+      <c r="G19" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H19" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="G19" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>89</v>
-      </c>
       <c r="I19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1685,28 +1702,28 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="D20" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" s="6" t="s">
+      <c r="G20" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H20" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>100</v>
-      </c>
       <c r="I20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1714,28 +1731,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="D21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>92</v>
-      </c>
       <c r="G21" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1743,26 +1760,26 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="D22" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1770,28 +1787,28 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="E23" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F23" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="F23" s="6" t="s">
+      <c r="G23" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="H23" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G23" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>10</v>
-      </c>
       <c r="I23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1799,19 +1816,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="D24" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="D24" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="14" t="s">
+      <c r="F24" s="15" t="s">
         <v>131</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>132</v>
       </c>
       <c r="G24">
         <v>123456</v>
@@ -1820,7 +1837,36 @@
         <v>18801376617</v>
       </c>
       <c r="I24" t="s">
-        <v>128</v>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="12">
+        <v>24</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G25">
+        <v>123456</v>
+      </c>
+      <c r="H25">
+        <v>12345678901</v>
+      </c>
+      <c r="I25" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1842,9 +1888,10 @@
     <hyperlink ref="F20" r:id="rId8" xr:uid="{20E5CA52-45F2-41B9-86A7-4DC99EC8F684}"/>
     <hyperlink ref="F21" r:id="rId9" xr:uid="{160233A7-DBBE-4E0E-B93C-C212C70C0B83}"/>
     <hyperlink ref="F24" r:id="rId10" xr:uid="{31B3FE49-1511-1541-BD48-B8F1EE9A3E05}"/>
+    <hyperlink ref="F25" r:id="rId11" xr:uid="{C23CFDA8-67CF-F34F-AFC7-8F7BFA4B6490}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId11"/>
+  <pageSetup orientation="portrait" r:id="rId12"/>
 </worksheet>
 </file>
 

--- a/users.xlsx
+++ b/users.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3A0063-6C34-0441-88E1-F909F00F84CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A95AFD3-B608-6847-AE98-7A7AEF6138B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="138">
   <si>
     <t>序号</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -138,9 +138,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>leo.liu@colliers.com</t>
-  </si>
-  <si>
     <t>18519772868</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -181,9 +178,6 @@
     <t>康磊</t>
   </si>
   <si>
-    <t>Jayden Kang</t>
-  </si>
-  <si>
     <t>jayden.kang@colliers.com</t>
   </si>
   <si>
@@ -230,12 +224,6 @@
   <si>
     <t>刘韵清</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lily Liu</t>
-  </si>
-  <si>
-    <t>lily.liu@colliers.com</t>
   </si>
   <si>
     <t>李嘉卉</t>
@@ -559,11 +547,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Full Name 
-(First/Middle/Last)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>张锐捷</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -577,6 +560,30 @@
   </si>
   <si>
     <t>123456@colliers.com</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jayden Kang</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lily Liu</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>leo.liu@colliers.com</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>lily.liu@colliers.com</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>18611510654</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Full Name </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -725,7 +732,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -734,47 +741,54 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="10" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1146,731 +1160,731 @@
     <col min="9" max="9" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32">
+    <row r="1" spans="1:9" ht="16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="F1" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="10" t="s">
-        <v>125</v>
+      <c r="I1" s="7" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="H2" s="9">
+      <c r="G2" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H2" s="11">
         <v>15210628244</v>
       </c>
       <c r="I2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="H3" s="9" t="s">
+      <c r="G3" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="H3" s="11" t="s">
         <v>20</v>
       </c>
       <c r="I3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>26</v>
-      </c>
       <c r="I4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H5" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>31</v>
-      </c>
       <c r="I5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="I6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="G7" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>40</v>
-      </c>
       <c r="I7" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="E8" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="F8" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H8" s="9">
+      <c r="G8" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H8" s="11">
         <v>17610772779</v>
       </c>
       <c r="I8" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="E9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="G9" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="H9" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>50</v>
-      </c>
       <c r="I9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="B10" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="H10" s="9">
-        <v>18611510654</v>
+      <c r="F10" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>136</v>
       </c>
       <c r="I10" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="B11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="H11" s="9">
+      <c r="E11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="H11" s="11">
         <v>17553833798</v>
       </c>
       <c r="I11" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="B12" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="H12" s="9">
+      <c r="E12" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H12" s="11">
         <v>18910329613</v>
       </c>
       <c r="I12" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="B13" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="H13" s="9">
+      <c r="E13" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="H13" s="11">
         <v>13911111029</v>
       </c>
       <c r="I13" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="B14" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>68</v>
+      <c r="F14" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>64</v>
       </c>
       <c r="I14" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" s="4" t="s">
+      <c r="B15" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="H15" s="9">
+      <c r="F15" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="H15" s="11">
         <v>13381036940</v>
       </c>
       <c r="I15" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="B16" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>76</v>
+      <c r="F16" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>72</v>
       </c>
       <c r="I16" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="B17" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>80</v>
+      <c r="E17" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="I17" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="B18" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>84</v>
+      <c r="F18" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="I18" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="B19" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F19" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="6" t="s">
+      <c r="F19" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="I19" t="s">
         <v>122</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="I19" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>99</v>
+      <c r="B20" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="I20" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" s="4" t="s">
+      <c r="B21" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F21" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="H21" s="9" t="s">
+      <c r="F21" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="12" t="s">
         <v>100</v>
       </c>
+      <c r="H21" s="11" t="s">
+        <v>96</v>
+      </c>
       <c r="I21" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E22" s="4" t="s">
+      <c r="B22" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9" t="s">
-        <v>95</v>
+      <c r="F22" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" s="12"/>
+      <c r="H22" s="11" t="s">
+        <v>91</v>
       </c>
       <c r="I22" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="F23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="C24" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="15" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="12">
+      <c r="F24" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="G24" s="16">
+        <v>123456</v>
+      </c>
+      <c r="H24" s="11">
+        <v>18801376617</v>
+      </c>
+      <c r="I24" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="14" t="s">
+      <c r="E25" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="F25" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="G24">
+      <c r="G25" s="16">
         <v>123456</v>
       </c>
-      <c r="H24">
-        <v>18801376617</v>
-      </c>
-      <c r="I24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="12">
-        <v>24</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="G25">
-        <v>123456</v>
-      </c>
-      <c r="H25">
+      <c r="H25" s="11">
         <v>12345678901</v>
       </c>
       <c r="I25" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A1:D1 F1:I1">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
@@ -1889,37 +1903,15 @@
     <hyperlink ref="F21" r:id="rId9" xr:uid="{160233A7-DBBE-4E0E-B93C-C212C70C0B83}"/>
     <hyperlink ref="F24" r:id="rId10" xr:uid="{31B3FE49-1511-1541-BD48-B8F1EE9A3E05}"/>
     <hyperlink ref="F25" r:id="rId11" xr:uid="{C23CFDA8-67CF-F34F-AFC7-8F7BFA4B6490}"/>
+    <hyperlink ref="F4" r:id="rId12" xr:uid="{D1DA91EE-2919-DF42-9EC9-B3255E182B67}"/>
+    <hyperlink ref="F10" r:id="rId13" xr:uid="{B650D25C-196E-CF48-BECD-678249574D0E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId12"/>
+  <pageSetup orientation="portrait" r:id="rId14"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="f655991e-a262-4cc2-969f-4b8d0db6a5de" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BC605E6093A30A479FED397EFA867E40" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55774fc2038cb4dae8fef12431c133f2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f655991e-a262-4cc2-969f-4b8d0db6a5de" xmlns:ns3="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="31482a63ce11ed8a627351d2502cc05d" ns2:_="" ns3:_="">
     <xsd:import namespace="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
@@ -2180,36 +2172,35 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"blankspreadsheet","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D06B2AC5-E0B1-41AB-AC8C-223291054D71}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{106A4909-FA24-4E21-8A33-CA1651A78349}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a"/>
-    <ds:schemaRef ds:uri="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f655991e-a262-4cc2-969f-4b8d0db6a5de" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E48FA878-1873-4E78-9DF6-64F409202FFB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDD333F8-AAE5-488E-AC14-BCEB9F667CC9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2228,9 +2219,34 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1DE854-5CA9-468B-A115-103B8CD51770}">
   <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D06B2AC5-E0B1-41AB-AC8C-223291054D71}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{106A4909-FA24-4E21-8A33-CA1651A78349}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a"/>
+    <ds:schemaRef ds:uri="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E48FA878-1873-4E78-9DF6-64F409202FFB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 

--- a/users.xlsx
+++ b/users.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A95AFD3-B608-6847-AE98-7A7AEF6138B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20CF2A73-A1E6-4BC7-A25D-460D9D48BCA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="139">
   <si>
     <t>序号</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -586,19 +586,22 @@
     <t xml:space="preserve">Full Name </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>15620895791</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="[$-409]mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]mmm\-yy;@"/>
   </numFmts>
   <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -610,14 +613,14 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -668,7 +671,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -760,13 +763,13 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -778,22 +781,22 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -1147,20 +1150,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1881D26D-58E6-4B13-B3DA-2DFBBC0E86E2}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.1640625" customWidth="1"/>
-    <col min="8" max="8" width="16.1640625" customWidth="1"/>
+    <col min="6" max="6" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.1796875" customWidth="1"/>
+    <col min="8" max="8" width="16.1796875" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16">
+    <row r="1" spans="1:9" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1788,7 +1791,9 @@
       <c r="F22" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="G22" s="12"/>
+      <c r="G22" s="11" t="s">
+        <v>138</v>
+      </c>
       <c r="H22" s="11" t="s">
         <v>91</v>
       </c>
@@ -1912,6 +1917,34 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f655991e-a262-4cc2-969f-4b8d0db6a5de" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"blankspreadsheet","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
+</file>
+
+<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BC605E6093A30A479FED397EFA867E40" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55774fc2038cb4dae8fef12431c133f2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f655991e-a262-4cc2-969f-4b8d0db6a5de" xmlns:ns3="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="31482a63ce11ed8a627351d2502cc05d" ns2:_="" ns3:_="">
     <xsd:import namespace="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
@@ -2172,35 +2205,38 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"blankspreadsheet","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E48FA878-1873-4E78-9DF6-64F409202FFB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{106A4909-FA24-4E21-8A33-CA1651A78349}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a"/>
+    <ds:schemaRef ds:uri="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="f655991e-a262-4cc2-969f-4b8d0db6a5de" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D06B2AC5-E0B1-41AB-AC8C-223291054D71}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1DE854-5CA9-468B-A115-103B8CD51770}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDD333F8-AAE5-488E-AC14-BCEB9F667CC9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2219,37 +2255,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1DE854-5CA9-468B-A115-103B8CD51770}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D06B2AC5-E0B1-41AB-AC8C-223291054D71}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{106A4909-FA24-4E21-8A33-CA1651A78349}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a"/>
-    <ds:schemaRef ds:uri="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E48FA878-1873-4E78-9DF6-64F409202FFB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{8c970d48-f7b9-48b0-9606-072fbefb514d}" enabled="1" method="Standard" siteId="{049e3382-8cdc-477b-9317-951b04689668}" contentBits="0" removed="0"/>
